--- a/api/templates/global_fund_inventory_report/vi.xlsx
+++ b/api/templates/global_fund_inventory_report/vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\maiki\.oh-my-zsh\aspect\api\templates\global_fund_inventory_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7746D5AD-ADE2-465D-9227-AEF264A585C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABBBF4A-80AF-40A1-9D73-C709690E9721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>STT</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Số lô</t>
   </si>
   <si>
-    <t>HSD</t>
-  </si>
-  <si>
     <t>Điều chuyển</t>
   </si>
   <si>
@@ -54,9 +51,6 @@
     <t>Tồn cuối</t>
   </si>
   <si>
-    <t>&lt;Dates&gt;</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -91,15 +85,38 @@
   </si>
   <si>
     <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>LGA: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>chứng khoán kỳ trước</t>
+  </si>
+  <si>
+    <t>ngày: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Những trạng thái: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Kiểm kê quỹ toàn cầu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,7 +132,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -129,16 +146,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -147,15 +164,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,12 +513,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
@@ -510,94 +528,98 @@
     <col min="10" max="10" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>6</v>
+      <c r="A3" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I8" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:I1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/api/templates/global_fund_inventory_report/vi.xlsx
+++ b/api/templates/global_fund_inventory_report/vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\maiki\.oh-my-zsh\aspect\api\templates\global_fund_inventory_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABBBF4A-80AF-40A1-9D73-C709690E9721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E48B90-7077-4614-8EFA-40DF87E0F199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,66 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>STT</t>
   </si>
   <si>
-    <t>Đơn Vị</t>
-  </si>
-  <si>
-    <t>Số lô</t>
-  </si>
-  <si>
-    <t>Điều chuyển</t>
-  </si>
-  <si>
-    <t>Sử dụng</t>
-  </si>
-  <si>
-    <t>Tồn cuối</t>
-  </si>
-  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
-    <t>&lt;lotNumber&gt;</t>
-  </si>
-  <si>
-    <t>&lt;expiresOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;stockLastMonth&gt;</t>
-  </si>
-  <si>
-    <t>&lt;transferFrom&gt;</t>
-  </si>
-  <si>
-    <t>&lt;receiveTo&gt;</t>
-  </si>
-  <si>
-    <t>&lt;use&gt;</t>
-  </si>
-  <si>
-    <t>&lt;damage&gt;</t>
-  </si>
-  <si>
-    <t>&lt;quantityOnHand&gt;</t>
-  </si>
-  <si>
-    <t>Tồn đầu kỳ</t>
-  </si>
-  <si>
-    <t>Nhập trong kỳ</t>
-  </si>
-  <si>
     <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>LGA: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>chứng khoán kỳ trước</t>
   </si>
   <si>
     <t>ngày: &lt;Dates&gt;</t>
@@ -530,27 +482,27 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -565,59 +517,19 @@
       <c r="A7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/api/templates/global_fund_inventory_report/vi.xlsx
+++ b/api/templates/global_fund_inventory_report/vi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\maiki\.oh-my-zsh\aspect\api\templates\global_fund_inventory_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ahernandez\repos\aspect\api\templates\global_fund_inventory_report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E48B90-7077-4614-8EFA-40DF87E0F199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEC9856-33B9-4030-BF49-E62F1D2FFC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +74,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -84,8 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF3CC0DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,10 +128,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -145,7 +150,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -466,9 +471,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="25.77734375" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -491,7 +496,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -513,8 +518,8 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
     </row>
